--- a/src/results/llm/actionable_feedback_01/results_for_presentation_actionable_feedback.xlsx
+++ b/src/results/llm/actionable_feedback_01/results_for_presentation_actionable_feedback.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\actionable_feedback_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B728AF75-C437-4550-A75B-4C340594E89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2C7863-239A-4774-A184-F36ABFE5B972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="37">
   <si>
     <t>Model</t>
   </si>
@@ -139,6 +139,15 @@
   </si>
   <si>
     <t>F1_macro diff</t>
+  </si>
+  <si>
+    <t>F1_macro diff to UP</t>
+  </si>
+  <si>
+    <t>F1_macro diff to RIGHT</t>
+  </si>
+  <si>
+    <t>Results if account for "nesaskaņas" where there were disrepancies in rubrics or human errors</t>
   </si>
 </sst>
 </file>
@@ -270,7 +279,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -278,27 +287,30 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="3" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="3" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="3"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -613,15 +625,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F8CBD-665F-4514-96E7-546603B512CB}">
-  <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P284"/>
+  <sheetFormatPr defaultRowHeight="16.5" thickTop="1" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.85546875" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" style="4" customWidth="1"/>
     <col min="3" max="3" width="15.140625" style="4" customWidth="1"/>
     <col min="4" max="4" width="17.140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" style="4" customWidth="1"/>
-    <col min="6" max="7" width="14.140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="17"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="23.7109375" customWidth="1"/>
@@ -635,49 +649,49 @@
     <col min="22" max="22" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:16" ht="36" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="11"/>
-      <c r="I1" s="10" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="7"/>
+      <c r="I1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
       <c r="O1"/>
       <c r="P1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="11"/>
-      <c r="I2" s="7" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="7"/>
+      <c r="I2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
       <c r="O2"/>
       <c r="P2"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -696,8 +710,8 @@
       <c r="F3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>33</v>
+      <c r="G3" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>0</v>
@@ -720,7 +734,7 @@
       <c r="O3"/>
       <c r="P3"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>30</v>
       </c>
@@ -739,7 +753,7 @@
       <c r="F4" s="4">
         <v>0.71742087603155802</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="9">
         <f>E4-M4</f>
         <v>-1.4080728968007938E-2</v>
       </c>
@@ -764,34 +778,34 @@
       <c r="O4"/>
       <c r="P4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="O5"/>
       <c r="P5"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="11"/>
-      <c r="I6" s="7" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="7"/>
+      <c r="I6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
       <c r="O6"/>
       <c r="P6"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>0</v>
       </c>
@@ -810,7 +824,7 @@
       <c r="F7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="12"/>
+      <c r="G7" s="3"/>
       <c r="I7" s="6" t="s">
         <v>0</v>
       </c>
@@ -832,7 +846,7 @@
       <c r="O7"/>
       <c r="P7"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>30</v>
       </c>
@@ -851,7 +865,7 @@
       <c r="F8" s="4">
         <v>0.53952168625861296</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="8">
         <f>E8-M8</f>
         <v>2.6433608084069915E-3</v>
       </c>
@@ -876,34 +890,34 @@
       <c r="O8"/>
       <c r="P8"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="O9"/>
       <c r="P9"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="11"/>
-      <c r="I10" s="7" t="s">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="7"/>
+      <c r="I10" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
       <c r="O10"/>
       <c r="P10"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>0</v>
       </c>
@@ -922,7 +936,7 @@
       <c r="F11" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="12"/>
+      <c r="G11" s="3"/>
       <c r="I11" s="6" t="s">
         <v>0</v>
       </c>
@@ -944,7 +958,7 @@
       <c r="O11"/>
       <c r="P11"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>30</v>
       </c>
@@ -963,7 +977,7 @@
       <c r="F12" s="4">
         <v>0.63491360212671599</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="9">
         <f>E12-M12</f>
         <v>-2.2019106641831931E-2</v>
       </c>
@@ -988,57 +1002,1301 @@
       <c r="O12"/>
       <c r="P12"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L13"/>
-      <c r="M13"/>
-      <c r="N13"/>
+    <row r="13" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
       <c r="O13"/>
       <c r="P13"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L14"/>
-      <c r="M14"/>
-      <c r="N14"/>
+    <row r="14" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="17"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
       <c r="O14"/>
       <c r="P14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="7"/>
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15"/>
       <c r="O15"/>
       <c r="P15"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="7"/>
       <c r="L16"/>
       <c r="M16"/>
       <c r="N16"/>
       <c r="O16"/>
       <c r="P16"/>
     </row>
-    <row r="17" spans="12:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="L17"/>
       <c r="M17"/>
       <c r="N17"/>
       <c r="O17"/>
       <c r="P17"/>
     </row>
-    <row r="18" spans="12:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="4">
+        <v>0.87878787878787801</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0.91620879120879095</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.89710827168796203</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0.86760175489159996</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.73538447534305795</v>
+      </c>
+      <c r="G18" s="8">
+        <f>E18-E4</f>
+        <v>8.9313690245619304E-3</v>
+      </c>
       <c r="L18"/>
       <c r="M18"/>
       <c r="N18"/>
       <c r="O18"/>
       <c r="P18"/>
     </row>
-    <row r="19" spans="12:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
       <c r="L19"/>
       <c r="M19"/>
       <c r="N19"/>
       <c r="O19"/>
       <c r="P19"/>
     </row>
+    <row r="20" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="4">
+        <v>0.69565217391304301</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0.92631578947368398</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.79458239277652298</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0.77353779656958499</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0.55784998481627701</v>
+      </c>
+      <c r="G22" s="8">
+        <f>E22-E8</f>
+        <v>8.7453767397469573E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+    </row>
+    <row r="24" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="4">
+        <v>0.89723320158102704</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0.85338345864661602</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.87475915221579903</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0.82595100467932803</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0.65229020394516801</v>
+      </c>
+      <c r="G26" s="8">
+        <f>E26-E12</f>
+        <v>8.8273709810640089E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="17"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+    </row>
+    <row r="28" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="G28"/>
+      <c r="H28"/>
+    </row>
+    <row r="29" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+      <c r="G29"/>
+      <c r="H29"/>
+    </row>
+    <row r="30" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+      <c r="G30"/>
+      <c r="H30"/>
+    </row>
+    <row r="31" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+      <c r="G31"/>
+      <c r="H31"/>
+    </row>
+    <row r="32" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+      <c r="G32"/>
+      <c r="H32"/>
+    </row>
+    <row r="33" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G33"/>
+      <c r="H33"/>
+    </row>
+    <row r="34" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G34"/>
+      <c r="H34"/>
+    </row>
+    <row r="35" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G35"/>
+      <c r="H35"/>
+    </row>
+    <row r="36" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G36"/>
+      <c r="H36"/>
+    </row>
+    <row r="37" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G37"/>
+      <c r="H37"/>
+    </row>
+    <row r="38" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G38"/>
+      <c r="H38"/>
+    </row>
+    <row r="39" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G39"/>
+      <c r="H39"/>
+    </row>
+    <row r="40" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G40"/>
+      <c r="H40"/>
+    </row>
+    <row r="41" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G41"/>
+      <c r="H41"/>
+    </row>
+    <row r="42" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G42"/>
+      <c r="H42"/>
+    </row>
+    <row r="43" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G43"/>
+      <c r="H43"/>
+    </row>
+    <row r="44" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G44"/>
+      <c r="H44"/>
+    </row>
+    <row r="45" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G45"/>
+      <c r="H45"/>
+    </row>
+    <row r="46" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G46"/>
+      <c r="H46"/>
+    </row>
+    <row r="47" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G47"/>
+      <c r="H47"/>
+    </row>
+    <row r="48" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G48"/>
+      <c r="H48"/>
+    </row>
+    <row r="49" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G49"/>
+      <c r="H49"/>
+    </row>
+    <row r="50" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G50"/>
+      <c r="H50"/>
+    </row>
+    <row r="51" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G51"/>
+      <c r="H51"/>
+    </row>
+    <row r="52" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G52"/>
+      <c r="H52"/>
+    </row>
+    <row r="53" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G53"/>
+      <c r="H53"/>
+    </row>
+    <row r="54" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G54"/>
+      <c r="H54"/>
+    </row>
+    <row r="55" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G55"/>
+      <c r="H55"/>
+    </row>
+    <row r="56" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G56"/>
+      <c r="H56"/>
+    </row>
+    <row r="57" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G57"/>
+      <c r="H57"/>
+    </row>
+    <row r="58" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G58"/>
+      <c r="H58"/>
+    </row>
+    <row r="59" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G59"/>
+      <c r="H59"/>
+    </row>
+    <row r="60" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G60"/>
+      <c r="H60"/>
+    </row>
+    <row r="61" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G61"/>
+      <c r="H61"/>
+    </row>
+    <row r="62" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G62"/>
+      <c r="H62"/>
+    </row>
+    <row r="63" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G63"/>
+      <c r="H63"/>
+    </row>
+    <row r="64" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G64"/>
+      <c r="H64"/>
+    </row>
+    <row r="65" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G65"/>
+      <c r="H65"/>
+    </row>
+    <row r="66" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G66"/>
+      <c r="H66"/>
+    </row>
+    <row r="67" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G67"/>
+      <c r="H67"/>
+    </row>
+    <row r="68" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G68"/>
+      <c r="H68"/>
+    </row>
+    <row r="69" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G69"/>
+      <c r="H69"/>
+    </row>
+    <row r="70" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G70"/>
+      <c r="H70"/>
+    </row>
+    <row r="71" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G71"/>
+      <c r="H71"/>
+    </row>
+    <row r="72" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G72"/>
+      <c r="H72"/>
+    </row>
+    <row r="73" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G73"/>
+      <c r="H73"/>
+    </row>
+    <row r="74" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G74"/>
+      <c r="H74"/>
+    </row>
+    <row r="75" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G75"/>
+      <c r="H75"/>
+    </row>
+    <row r="76" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G76"/>
+      <c r="H76"/>
+    </row>
+    <row r="77" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G77"/>
+      <c r="H77"/>
+    </row>
+    <row r="78" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G78"/>
+      <c r="H78"/>
+    </row>
+    <row r="79" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G79"/>
+      <c r="H79"/>
+    </row>
+    <row r="80" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G80"/>
+      <c r="H80"/>
+    </row>
+    <row r="81" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G81"/>
+      <c r="H81"/>
+    </row>
+    <row r="82" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G82"/>
+      <c r="H82"/>
+    </row>
+    <row r="83" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G83"/>
+      <c r="H83"/>
+    </row>
+    <row r="84" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G84"/>
+      <c r="H84"/>
+    </row>
+    <row r="85" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G85"/>
+      <c r="H85"/>
+    </row>
+    <row r="86" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G86"/>
+      <c r="H86"/>
+    </row>
+    <row r="87" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G87"/>
+      <c r="H87"/>
+    </row>
+    <row r="88" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G88"/>
+      <c r="H88"/>
+    </row>
+    <row r="89" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G89"/>
+      <c r="H89"/>
+    </row>
+    <row r="90" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G90"/>
+      <c r="H90"/>
+    </row>
+    <row r="91" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G91"/>
+      <c r="H91"/>
+    </row>
+    <row r="92" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G92"/>
+      <c r="H92"/>
+    </row>
+    <row r="93" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G93"/>
+      <c r="H93"/>
+    </row>
+    <row r="94" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G94"/>
+      <c r="H94"/>
+    </row>
+    <row r="95" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G95"/>
+      <c r="H95"/>
+    </row>
+    <row r="96" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G96"/>
+      <c r="H96"/>
+    </row>
+    <row r="97" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G97"/>
+      <c r="H97"/>
+    </row>
+    <row r="98" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G98"/>
+      <c r="H98"/>
+    </row>
+    <row r="99" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G99"/>
+      <c r="H99"/>
+    </row>
+    <row r="100" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G100"/>
+      <c r="H100"/>
+    </row>
+    <row r="101" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G101"/>
+      <c r="H101"/>
+    </row>
+    <row r="102" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G102"/>
+      <c r="H102"/>
+    </row>
+    <row r="103" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G103"/>
+      <c r="H103"/>
+    </row>
+    <row r="104" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G104"/>
+      <c r="H104"/>
+    </row>
+    <row r="105" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G105"/>
+      <c r="H105"/>
+    </row>
+    <row r="106" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G106"/>
+      <c r="H106"/>
+    </row>
+    <row r="107" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G107"/>
+      <c r="H107"/>
+    </row>
+    <row r="108" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G108"/>
+      <c r="H108"/>
+    </row>
+    <row r="109" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G109"/>
+      <c r="H109"/>
+    </row>
+    <row r="110" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G110"/>
+      <c r="H110"/>
+    </row>
+    <row r="111" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G111"/>
+      <c r="H111"/>
+    </row>
+    <row r="112" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G112"/>
+      <c r="H112"/>
+    </row>
+    <row r="113" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G113"/>
+      <c r="H113"/>
+    </row>
+    <row r="114" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G114"/>
+      <c r="H114"/>
+    </row>
+    <row r="115" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G115"/>
+      <c r="H115"/>
+    </row>
+    <row r="116" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G116"/>
+      <c r="H116"/>
+    </row>
+    <row r="117" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G117"/>
+      <c r="H117"/>
+    </row>
+    <row r="118" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G118"/>
+      <c r="H118"/>
+    </row>
+    <row r="119" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G119"/>
+      <c r="H119"/>
+    </row>
+    <row r="120" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G120"/>
+      <c r="H120"/>
+    </row>
+    <row r="121" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G121"/>
+      <c r="H121"/>
+    </row>
+    <row r="122" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G122"/>
+      <c r="H122"/>
+    </row>
+    <row r="123" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G123"/>
+      <c r="H123"/>
+    </row>
+    <row r="124" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G124"/>
+      <c r="H124"/>
+    </row>
+    <row r="125" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G125"/>
+      <c r="H125"/>
+    </row>
+    <row r="126" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G126"/>
+      <c r="H126"/>
+    </row>
+    <row r="127" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G127"/>
+      <c r="H127"/>
+    </row>
+    <row r="128" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G128"/>
+      <c r="H128"/>
+    </row>
+    <row r="129" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G129"/>
+      <c r="H129"/>
+    </row>
+    <row r="130" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G130"/>
+      <c r="H130"/>
+    </row>
+    <row r="131" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G131"/>
+      <c r="H131"/>
+    </row>
+    <row r="132" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G132"/>
+      <c r="H132"/>
+    </row>
+    <row r="133" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G133"/>
+      <c r="H133"/>
+    </row>
+    <row r="134" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G134"/>
+      <c r="H134"/>
+    </row>
+    <row r="135" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G135"/>
+      <c r="H135"/>
+    </row>
+    <row r="136" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G136"/>
+      <c r="H136"/>
+    </row>
+    <row r="137" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G137"/>
+      <c r="H137"/>
+    </row>
+    <row r="138" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G138"/>
+      <c r="H138"/>
+    </row>
+    <row r="139" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G139"/>
+      <c r="H139"/>
+    </row>
+    <row r="140" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G140"/>
+      <c r="H140"/>
+    </row>
+    <row r="141" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G141"/>
+      <c r="H141"/>
+    </row>
+    <row r="142" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G142"/>
+      <c r="H142"/>
+    </row>
+    <row r="143" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G143"/>
+      <c r="H143"/>
+    </row>
+    <row r="144" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G144"/>
+      <c r="H144"/>
+    </row>
+    <row r="145" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G145"/>
+      <c r="H145"/>
+    </row>
+    <row r="146" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G146"/>
+      <c r="H146"/>
+    </row>
+    <row r="147" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G147"/>
+      <c r="H147"/>
+    </row>
+    <row r="148" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G148"/>
+      <c r="H148"/>
+    </row>
+    <row r="149" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G149"/>
+      <c r="H149"/>
+    </row>
+    <row r="150" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G150"/>
+      <c r="H150"/>
+    </row>
+    <row r="151" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G151"/>
+      <c r="H151"/>
+    </row>
+    <row r="152" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G152"/>
+      <c r="H152"/>
+    </row>
+    <row r="153" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G153"/>
+      <c r="H153"/>
+    </row>
+    <row r="154" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G154"/>
+      <c r="H154"/>
+    </row>
+    <row r="155" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G155"/>
+      <c r="H155"/>
+    </row>
+    <row r="156" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G156"/>
+      <c r="H156"/>
+    </row>
+    <row r="157" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G157"/>
+      <c r="H157"/>
+    </row>
+    <row r="158" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G158"/>
+      <c r="H158"/>
+    </row>
+    <row r="159" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G159"/>
+      <c r="H159"/>
+    </row>
+    <row r="160" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G160"/>
+      <c r="H160"/>
+    </row>
+    <row r="161" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G161"/>
+      <c r="H161"/>
+    </row>
+    <row r="162" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G162"/>
+      <c r="H162"/>
+    </row>
+    <row r="163" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G163"/>
+      <c r="H163"/>
+    </row>
+    <row r="164" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G164"/>
+      <c r="H164"/>
+    </row>
+    <row r="165" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G165"/>
+      <c r="H165"/>
+    </row>
+    <row r="166" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G166"/>
+      <c r="H166"/>
+    </row>
+    <row r="167" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G167"/>
+      <c r="H167"/>
+    </row>
+    <row r="168" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G168"/>
+      <c r="H168"/>
+    </row>
+    <row r="169" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G169"/>
+      <c r="H169"/>
+    </row>
+    <row r="170" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G170"/>
+      <c r="H170"/>
+    </row>
+    <row r="171" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G171"/>
+      <c r="H171"/>
+    </row>
+    <row r="172" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G172"/>
+      <c r="H172"/>
+    </row>
+    <row r="173" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G173"/>
+      <c r="H173"/>
+    </row>
+    <row r="174" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G174"/>
+      <c r="H174"/>
+    </row>
+    <row r="175" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G175"/>
+      <c r="H175"/>
+    </row>
+    <row r="176" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G176"/>
+      <c r="H176"/>
+    </row>
+    <row r="177" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G177"/>
+      <c r="H177"/>
+    </row>
+    <row r="178" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G178"/>
+      <c r="H178"/>
+    </row>
+    <row r="179" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G179"/>
+      <c r="H179"/>
+    </row>
+    <row r="180" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G180"/>
+      <c r="H180"/>
+    </row>
+    <row r="181" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G181"/>
+      <c r="H181"/>
+    </row>
+    <row r="182" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G182"/>
+      <c r="H182"/>
+    </row>
+    <row r="183" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G183"/>
+      <c r="H183"/>
+    </row>
+    <row r="184" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G184"/>
+      <c r="H184"/>
+    </row>
+    <row r="185" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G185"/>
+      <c r="H185"/>
+    </row>
+    <row r="186" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G186"/>
+      <c r="H186"/>
+    </row>
+    <row r="187" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G187"/>
+      <c r="H187"/>
+    </row>
+    <row r="188" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G188"/>
+      <c r="H188"/>
+    </row>
+    <row r="189" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G189"/>
+      <c r="H189"/>
+    </row>
+    <row r="190" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G190"/>
+      <c r="H190"/>
+    </row>
+    <row r="191" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G191"/>
+      <c r="H191"/>
+    </row>
+    <row r="192" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G192"/>
+      <c r="H192"/>
+    </row>
+    <row r="193" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G193"/>
+      <c r="H193"/>
+    </row>
+    <row r="194" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G194"/>
+      <c r="H194"/>
+    </row>
+    <row r="195" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G195"/>
+      <c r="H195"/>
+    </row>
+    <row r="196" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G196"/>
+      <c r="H196"/>
+    </row>
+    <row r="197" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G197"/>
+      <c r="H197"/>
+    </row>
+    <row r="198" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G198"/>
+      <c r="H198"/>
+    </row>
+    <row r="199" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G199"/>
+      <c r="H199"/>
+    </row>
+    <row r="200" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G200"/>
+      <c r="H200"/>
+    </row>
+    <row r="201" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G201"/>
+      <c r="H201"/>
+    </row>
+    <row r="202" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G202"/>
+      <c r="H202"/>
+    </row>
+    <row r="203" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G203"/>
+      <c r="H203"/>
+    </row>
+    <row r="204" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G204"/>
+      <c r="H204"/>
+    </row>
+    <row r="205" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G205"/>
+      <c r="H205"/>
+    </row>
+    <row r="206" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G206"/>
+      <c r="H206"/>
+    </row>
+    <row r="207" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G207"/>
+      <c r="H207"/>
+    </row>
+    <row r="208" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G208"/>
+      <c r="H208"/>
+    </row>
+    <row r="209" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G209"/>
+      <c r="H209"/>
+    </row>
+    <row r="210" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G210"/>
+      <c r="H210"/>
+    </row>
+    <row r="211" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G211"/>
+      <c r="H211"/>
+    </row>
+    <row r="212" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G212"/>
+      <c r="H212"/>
+    </row>
+    <row r="213" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G213"/>
+      <c r="H213"/>
+    </row>
+    <row r="214" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G214"/>
+      <c r="H214"/>
+    </row>
+    <row r="215" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G215"/>
+      <c r="H215"/>
+    </row>
+    <row r="216" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G216"/>
+      <c r="H216"/>
+    </row>
+    <row r="217" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G217"/>
+      <c r="H217"/>
+    </row>
+    <row r="218" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G218"/>
+      <c r="H218"/>
+    </row>
+    <row r="219" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G219"/>
+      <c r="H219"/>
+    </row>
+    <row r="220" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G220"/>
+      <c r="H220"/>
+    </row>
+    <row r="221" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G221"/>
+      <c r="H221"/>
+    </row>
+    <row r="222" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G222"/>
+      <c r="H222"/>
+    </row>
+    <row r="223" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G223"/>
+      <c r="H223"/>
+    </row>
+    <row r="224" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G224"/>
+      <c r="H224"/>
+    </row>
+    <row r="225" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G225"/>
+      <c r="H225"/>
+    </row>
+    <row r="226" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G226"/>
+      <c r="H226"/>
+    </row>
+    <row r="227" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G227"/>
+      <c r="H227"/>
+    </row>
+    <row r="228" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G228"/>
+      <c r="H228"/>
+    </row>
+    <row r="229" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G229"/>
+      <c r="H229"/>
+    </row>
+    <row r="230" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G230"/>
+      <c r="H230"/>
+    </row>
+    <row r="231" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G231"/>
+      <c r="H231"/>
+    </row>
+    <row r="232" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G232"/>
+      <c r="H232"/>
+    </row>
+    <row r="233" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G233"/>
+      <c r="H233"/>
+    </row>
+    <row r="234" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G234"/>
+      <c r="H234"/>
+    </row>
+    <row r="235" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G235"/>
+      <c r="H235"/>
+    </row>
+    <row r="236" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G236"/>
+      <c r="H236"/>
+    </row>
+    <row r="237" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G237"/>
+      <c r="H237"/>
+    </row>
+    <row r="238" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G238"/>
+      <c r="H238"/>
+    </row>
+    <row r="239" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G239"/>
+      <c r="H239"/>
+    </row>
+    <row r="240" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G240"/>
+      <c r="H240"/>
+    </row>
+    <row r="241" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G241"/>
+      <c r="H241"/>
+    </row>
+    <row r="242" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G242"/>
+      <c r="H242"/>
+    </row>
+    <row r="243" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G243"/>
+      <c r="H243"/>
+    </row>
+    <row r="244" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G244"/>
+      <c r="H244"/>
+    </row>
+    <row r="245" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G245"/>
+      <c r="H245"/>
+    </row>
+    <row r="246" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G246"/>
+      <c r="H246"/>
+    </row>
+    <row r="247" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G247"/>
+      <c r="H247"/>
+    </row>
+    <row r="248" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G248"/>
+      <c r="H248"/>
+    </row>
+    <row r="249" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G249"/>
+      <c r="H249"/>
+    </row>
+    <row r="250" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G250"/>
+      <c r="H250"/>
+    </row>
+    <row r="251" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G251"/>
+      <c r="H251"/>
+    </row>
+    <row r="252" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G252"/>
+      <c r="H252"/>
+    </row>
+    <row r="253" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G253"/>
+      <c r="H253"/>
+    </row>
+    <row r="254" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G254"/>
+      <c r="H254"/>
+    </row>
+    <row r="255" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G255"/>
+      <c r="H255"/>
+    </row>
+    <row r="256" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G256"/>
+      <c r="H256"/>
+    </row>
+    <row r="257" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G257"/>
+      <c r="H257"/>
+    </row>
+    <row r="258" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G258"/>
+      <c r="H258"/>
+    </row>
+    <row r="259" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G259"/>
+      <c r="H259"/>
+    </row>
+    <row r="260" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G260"/>
+      <c r="H260"/>
+    </row>
+    <row r="261" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G261"/>
+      <c r="H261"/>
+    </row>
+    <row r="262" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G262"/>
+      <c r="H262"/>
+    </row>
+    <row r="263" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G263"/>
+      <c r="H263"/>
+    </row>
+    <row r="264" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G264"/>
+      <c r="H264"/>
+    </row>
+    <row r="265" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G265"/>
+      <c r="H265"/>
+    </row>
+    <row r="266" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G266"/>
+      <c r="H266"/>
+    </row>
+    <row r="267" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G267"/>
+      <c r="H267"/>
+    </row>
+    <row r="268" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G268"/>
+      <c r="H268"/>
+    </row>
+    <row r="269" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G269"/>
+      <c r="H269"/>
+    </row>
+    <row r="270" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G270"/>
+      <c r="H270"/>
+    </row>
+    <row r="271" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G271"/>
+      <c r="H271"/>
+    </row>
+    <row r="272" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G272"/>
+      <c r="H272"/>
+    </row>
+    <row r="273" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G273"/>
+      <c r="H273"/>
+    </row>
+    <row r="274" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G274"/>
+      <c r="H274"/>
+    </row>
+    <row r="275" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G275"/>
+      <c r="H275"/>
+    </row>
+    <row r="276" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G276"/>
+      <c r="H276"/>
+    </row>
+    <row r="277" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G277"/>
+      <c r="H277"/>
+    </row>
+    <row r="278" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G278"/>
+      <c r="H278"/>
+    </row>
+    <row r="279" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G279"/>
+      <c r="H279"/>
+    </row>
+    <row r="280" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G280"/>
+      <c r="H280"/>
+    </row>
+    <row r="281" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G281"/>
+      <c r="H281"/>
+    </row>
+    <row r="282" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G282"/>
+      <c r="H282"/>
+    </row>
+    <row r="283" spans="7:8" ht="15" x14ac:dyDescent="0.25">
+      <c r="G283"/>
+      <c r="H283"/>
+    </row>
+    <row r="284" spans="7:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G284"/>
+      <c r="H284"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="12">
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A10:F10"/>
@@ -1125,7 +2383,7 @@
     <col min="5" max="5" width="16.28515625" style="4" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" style="4" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="17"/>
+    <col min="8" max="8" width="9.140625" style="12"/>
     <col min="9" max="9" width="18.7109375" style="4" customWidth="1"/>
     <col min="10" max="10" width="23.85546875" style="4" customWidth="1"/>
     <col min="11" max="11" width="20.140625" style="4" customWidth="1"/>
@@ -1136,41 +2394,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="37.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="I1" s="10" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="I1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="15"/>
-      <c r="I2" s="9" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="10"/>
+      <c r="I2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1192,7 +2450,7 @@
       <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="11" t="s">
         <v>33</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -1234,7 +2492,7 @@
       <c r="F4" s="4">
         <v>0.88170055452865004</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="10">
         <f>E4-M4</f>
         <v>0</v>
       </c>
@@ -1276,7 +2534,7 @@
       <c r="F5" s="4">
         <v>0.316239316239316</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="10">
         <f t="shared" ref="G5:G23" si="0">E5-M5</f>
         <v>3.9801531173526028E-2</v>
       </c>
@@ -1318,7 +2576,7 @@
       <c r="F6" s="4">
         <v>0.72481572481572398</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="10">
         <f t="shared" si="0"/>
         <v>4.6097648814116932E-2</v>
       </c>
@@ -1360,7 +2618,7 @@
       <c r="F7" s="4">
         <v>0.70608495981630304</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1402,7 +2660,7 @@
       <c r="F8" s="4">
         <v>0.61599999999999999</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="10">
         <f t="shared" si="0"/>
         <v>-9.8074545133368995E-2</v>
       </c>
@@ -1444,7 +2702,7 @@
       <c r="F9" s="4">
         <v>0.55778894472361795</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="10">
         <f t="shared" si="0"/>
         <v>-2.3934444261123011E-2</v>
       </c>
@@ -1486,7 +2744,7 @@
       <c r="F10" s="4">
         <v>0.42536475869809198</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="10">
         <f t="shared" si="0"/>
         <v>-5.9114829209025999E-2</v>
       </c>
@@ -1528,7 +2786,7 @@
       <c r="F11" s="4">
         <v>0.89743589743589702</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1570,7 +2828,7 @@
       <c r="F12" s="4">
         <v>0.24110671936758801</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="10">
         <f t="shared" si="0"/>
         <v>-6.1540770760628027E-2</v>
       </c>
@@ -1612,7 +2870,7 @@
       <c r="F13" s="4">
         <v>1</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1654,7 +2912,7 @@
       <c r="F14" s="4">
         <v>1</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1696,7 +2954,7 @@
       <c r="F15" s="4">
         <v>0.25512104283053999</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="10">
         <f t="shared" si="0"/>
         <v>-1.2071446117135953E-2</v>
       </c>
@@ -1738,7 +2996,7 @@
       <c r="F16" s="4">
         <v>0.85746102449888595</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="10">
         <f t="shared" si="0"/>
         <v>-7.1428571428571952E-2</v>
       </c>
@@ -1780,7 +3038,7 @@
       <c r="F17" s="4">
         <v>0.81467181467181404</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="10">
         <f t="shared" si="0"/>
         <v>9.0399713201999576E-3</v>
       </c>
@@ -1822,7 +3080,7 @@
       <c r="F18" s="4">
         <v>0.439824945295404</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="10">
         <f t="shared" si="0"/>
         <v>-2.1407501053519074E-2</v>
       </c>
@@ -1864,7 +3122,7 @@
       <c r="F19" s="4">
         <v>0.371779141104294</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="10">
         <f t="shared" si="0"/>
         <v>2.7898819102109007E-2</v>
       </c>
@@ -1906,7 +3164,7 @@
       <c r="F20" s="4">
         <v>0.96199524940617498</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1948,7 +3206,7 @@
       <c r="F21" s="4">
         <v>0.6</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="10">
         <f t="shared" si="0"/>
         <v>-0.12752304016384097</v>
       </c>
@@ -1990,7 +3248,7 @@
       <c r="F22" s="4">
         <v>0.92</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="10">
         <f t="shared" si="0"/>
         <v>5.4990032461872063E-2</v>
       </c>
@@ -2032,7 +3290,7 @@
       <c r="F23" s="4">
         <v>0.66249421544380505</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="10">
         <f t="shared" si="0"/>
         <v>-1.5645639223968E-2</v>
       </c>
@@ -2060,23 +3318,23 @@
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:14" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
       <c r="G25"/>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
     </row>
     <row r="26" spans="1:14" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
@@ -2097,7 +3355,7 @@
       <c r="F26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="11" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -2138,7 +3396,7 @@
       <c r="F27" s="4">
         <v>0.45165238678090502</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="10">
         <f>E27-M27</f>
         <v>0</v>
       </c>
@@ -2180,7 +3438,7 @@
       <c r="F28" s="4">
         <v>0.53674832962137997</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="10">
         <f t="shared" ref="G28:G46" si="1">E28-M28</f>
         <v>-2.5457021251807044E-2</v>
       </c>
@@ -2222,7 +3480,7 @@
       <c r="F29" s="4">
         <v>0.38238841978287003</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="10">
         <f t="shared" si="1"/>
         <v>-2.882830591379304E-2</v>
       </c>
@@ -2264,7 +3522,7 @@
       <c r="F30" s="4">
         <v>2.67921795800144E-2</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2306,7 +3564,7 @@
       <c r="F31" s="4">
         <v>0.62790697674418605</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="10">
         <f t="shared" si="1"/>
         <v>5.5974138468823931E-2</v>
       </c>
@@ -2348,7 +3606,7 @@
       <c r="F32" s="4">
         <v>0.41312741312741302</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="10">
         <f t="shared" si="1"/>
         <v>4.1285157005242934E-2</v>
       </c>
@@ -2390,7 +3648,7 @@
       <c r="F33" s="4">
         <v>0.36960600375234498</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="10">
         <f t="shared" si="1"/>
         <v>6.4818698864387958E-2</v>
       </c>
@@ -2432,7 +3690,7 @@
       <c r="F34" s="4">
         <v>0.43568464730290402</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2474,7 +3732,7 @@
       <c r="F35" s="4">
         <v>0.32046332046331999</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="10">
         <f t="shared" si="1"/>
         <v>1.6483881688267976E-2</v>
       </c>
@@ -2516,7 +3774,7 @@
       <c r="F36" s="4">
         <v>1</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2558,7 +3816,7 @@
       <c r="F37" s="4">
         <v>1</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2600,7 +3858,7 @@
       <c r="F38" s="4">
         <v>8.8607594936708806E-2</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="10">
         <f t="shared" si="1"/>
         <v>4.9540396710209822E-3</v>
       </c>
@@ -2642,7 +3900,7 @@
       <c r="F39" s="4">
         <v>0.69111969111969096</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="10">
         <f t="shared" si="1"/>
         <v>-5.2765919553773966E-2</v>
       </c>
@@ -2684,7 +3942,7 @@
       <c r="F40" s="4">
         <v>0.87096774193548299</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="10">
         <f t="shared" si="1"/>
         <v>6.7821067821070002E-3</v>
       </c>
@@ -2726,7 +3984,7 @@
       <c r="F41" s="4">
         <v>0.18053777208706701</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="10">
         <f t="shared" si="1"/>
         <v>-1.1231599350411958E-2</v>
       </c>
@@ -2768,7 +4026,7 @@
       <c r="F42" s="4">
         <v>0.291139240506329</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="10">
         <f t="shared" si="1"/>
         <v>2.238118302037595E-2</v>
       </c>
@@ -2810,7 +4068,7 @@
       <c r="F43" s="4">
         <v>0.797468354430379</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2852,7 +4110,7 @@
       <c r="F44" s="4">
         <v>0.69230769230769196</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="10">
         <f t="shared" si="1"/>
         <v>-0.11915194119440897</v>
       </c>
@@ -2894,7 +4152,7 @@
       <c r="F45" s="4">
         <v>0.463687150837988</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="10">
         <f t="shared" si="1"/>
         <v>2.4020143474750011E-3</v>
       </c>
@@ -2936,7 +4194,7 @@
       <c r="F46" s="4">
         <v>0.50737920606929898</v>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="10">
         <f t="shared" si="1"/>
         <v>-1.1765035482369512E-3</v>
       </c>
@@ -2960,27 +4218,27 @@
       </c>
     </row>
     <row r="47" spans="1:14" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G47" s="15"/>
+      <c r="G47" s="10"/>
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:14" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="15"/>
-      <c r="I48" s="9" t="s">
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="10"/>
+      <c r="I48" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-      <c r="M48" s="9"/>
-      <c r="N48" s="9"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
     </row>
     <row r="49" spans="1:14" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
@@ -3001,7 +4259,7 @@
       <c r="F49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G49" s="16" t="s">
+      <c r="G49" s="11" t="s">
         <v>33</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -3042,7 +4300,7 @@
       <c r="F50" s="4">
         <v>0.82978723404255295</v>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="10">
         <f>E50-M50</f>
         <v>0</v>
       </c>
@@ -3084,7 +4342,7 @@
       <c r="F51" s="4">
         <v>0.465478841870824</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="10">
         <f t="shared" ref="G51:G69" si="2">E51-M51</f>
         <v>-9.5973552659843087E-2</v>
       </c>
@@ -3126,7 +4384,7 @@
       <c r="F52" s="4">
         <v>0.231385108086469</v>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="10">
         <f t="shared" si="2"/>
         <v>3.1738758553275015E-2</v>
       </c>
@@ -3168,7 +4426,7 @@
       <c r="F53" s="4">
         <v>0.75032509752925802</v>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3210,7 +4468,7 @@
       <c r="F54" s="4">
         <v>0.66804979253111996</v>
       </c>
-      <c r="G54" s="15">
+      <c r="G54" s="10">
         <f t="shared" si="2"/>
         <v>2.5525525525526005E-2</v>
       </c>
@@ -3252,7 +4510,7 @@
       <c r="F55" s="4">
         <v>0.425414364640884</v>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="10">
         <f t="shared" si="2"/>
         <v>-6.6587859614118949E-2</v>
       </c>
@@ -3294,7 +4552,7 @@
       <c r="F56" s="4">
         <v>0.33402705515088399</v>
       </c>
-      <c r="G56" s="15">
+      <c r="G56" s="10">
         <f t="shared" si="2"/>
         <v>-2.1645021645022022E-2</v>
       </c>
@@ -3336,7 +4594,7 @@
       <c r="F57" s="4">
         <v>0.157894736842105</v>
       </c>
-      <c r="G57" s="15">
+      <c r="G57" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3378,7 +4636,7 @@
       <c r="F58" s="4">
         <v>0.28744939271254999</v>
       </c>
-      <c r="G58" s="15">
+      <c r="G58" s="10">
         <f t="shared" si="2"/>
         <v>-0.12534562211981504</v>
       </c>
@@ -3420,7 +4678,7 @@
       <c r="F59" s="4">
         <v>0.95744680851063801</v>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3462,7 +4720,7 @@
       <c r="F60" s="4">
         <v>1</v>
       </c>
-      <c r="G60" s="15">
+      <c r="G60" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3504,7 +4762,7 @@
       <c r="F61" s="4">
         <v>0.34693877551020402</v>
       </c>
-      <c r="G61" s="15">
+      <c r="G61" s="10">
         <f t="shared" si="2"/>
         <v>-4.3202143343585964E-2</v>
       </c>
@@ -3546,7 +4804,7 @@
       <c r="F62" s="4">
         <v>0.79661016949152497</v>
       </c>
-      <c r="G62" s="15">
+      <c r="G62" s="10">
         <f t="shared" si="2"/>
         <v>-6.3990695536765063E-2</v>
       </c>
@@ -3588,7 +4846,7 @@
       <c r="F63" s="4">
         <v>0.81467181467181404</v>
       </c>
-      <c r="G63" s="15">
+      <c r="G63" s="10">
         <f t="shared" si="2"/>
         <v>9.0399713201999576E-3</v>
       </c>
@@ -3630,7 +4888,7 @@
       <c r="F64" s="4">
         <v>0.29729729729729698</v>
       </c>
-      <c r="G64" s="15">
+      <c r="G64" s="10">
         <f t="shared" si="2"/>
         <v>-1.4715917519656063E-2</v>
       </c>
@@ -3672,7 +4930,7 @@
       <c r="F65" s="4">
         <v>0.499021526418786</v>
       </c>
-      <c r="G65" s="15">
+      <c r="G65" s="10">
         <f t="shared" si="2"/>
         <v>-9.8184856079593041E-2</v>
       </c>
@@ -3714,7 +4972,7 @@
       <c r="F66" s="4">
         <v>0.92514619883040905</v>
       </c>
-      <c r="G66" s="15">
+      <c r="G66" s="10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3756,7 +5014,7 @@
       <c r="F67" s="4">
         <v>0.64705882352941102</v>
       </c>
-      <c r="G67" s="15">
+      <c r="G67" s="10">
         <f t="shared" si="2"/>
         <v>-8.7247283405616938E-2</v>
       </c>
@@ -3798,7 +5056,7 @@
       <c r="F68" s="4">
         <v>0.84541062801932298</v>
       </c>
-      <c r="G68" s="15">
+      <c r="G68" s="10">
         <f t="shared" si="2"/>
         <v>1.4897765752675096E-2</v>
       </c>
@@ -3840,7 +5098,7 @@
       <c r="F69" s="4">
         <v>0.59365335082558202</v>
       </c>
-      <c r="G69" s="15">
+      <c r="G69" s="10">
         <f t="shared" si="2"/>
         <v>-2.8194259514333964E-2</v>
       </c>
@@ -3874,6 +5132,29 @@
     <mergeCell ref="I25:N25"/>
     <mergeCell ref="I48:N48"/>
   </mergeCells>
+  <conditionalFormatting sqref="B1:F1048576">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G23 G26:G46 G49:G69 G145:G1048576">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J2:N2">
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -3898,29 +5179,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:F1048576">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G23 G26:G46 G49:G69 G145:G1048576">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>